--- a/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/monica_cruz_gifseguridad_com_mx/Documents/Escritorio/REPORTES DEDUCCIONES/DEDUCCIONESNOMINA2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C51CC929-5429-4E9A-975F-04CB406B625C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFC2F1F5-B653-4526-A387-970DB8107945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/monica_cruz_gifseguridad_com_mx/Documents/Escritorio/REPORTES DEDUCCIONES/DEDUCCIONESNOMINA2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/monica_cruz_gifseguridad_com_mx/Documents/Escritorio/REPORTES DEDUCCIONES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFC2F1F5-B653-4526-A387-970DB8107945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FADEB8EF-A1E9-4863-9C75-6EFC672F163B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>09-0001-02</t>
   </si>
@@ -52,6 +52,12 @@
     <t>ROSAS ROSAS LUIS ENRIQUE</t>
   </si>
   <si>
+    <t>09-0024-02</t>
+  </si>
+  <si>
+    <t>BOHNE LOPEZ CINTIA STEPHANIE</t>
+  </si>
+  <si>
     <t>09-0244-03</t>
   </si>
   <si>
@@ -148,16 +154,16 @@
     <t>MEDINA ALVAREZ KARLA ITZEL</t>
   </si>
   <si>
+    <t>09-0410-03</t>
+  </si>
+  <si>
+    <t>CORREA MARTINEZ JOSE LUIS</t>
+  </si>
+  <si>
     <t>15-0016-03</t>
   </si>
   <si>
     <t>OSORIO MIRANDA REYNA</t>
-  </si>
-  <si>
-    <t>15-0023-03</t>
-  </si>
-  <si>
-    <t>ALAMILLO CHAVEZ RAYMUNDO</t>
   </si>
   <si>
     <t>15-0024-03</t>
@@ -570,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
@@ -760,7 +766,7 @@
         <v>33</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>352.19</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -903,6 +909,17 @@
         <v>59</v>
       </c>
       <c r="C30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31">
         <v>0</v>
       </c>
     </row>

--- a/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/monica_cruz_gifseguridad_com_mx/Documents/Escritorio/REPORTES DEDUCCIONES/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/monica_cruz_gifseguridad_com_mx/Documents/Escritorio/REPORTES DEDUCCIONES/DEDUCCIONESNOMINA2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FADEB8EF-A1E9-4863-9C75-6EFC672F163B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5C8B74C-765D-469E-9D8E-4607FBD7DD8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>09-0001-02</t>
   </si>
@@ -82,12 +82,6 @@
     <t>HERNANDEZ SOSA JOSE GUADALUPE</t>
   </si>
   <si>
-    <t>09-0368-03</t>
-  </si>
-  <si>
-    <t>ESPINOZA RUIZ ROSA MARIA</t>
-  </si>
-  <si>
     <t>09-0369-03</t>
   </si>
   <si>
@@ -112,12 +106,6 @@
     <t>ITURBIDE JIMENEZ JUAN JESUS</t>
   </si>
   <si>
-    <t>09-0394-03</t>
-  </si>
-  <si>
-    <t>SANTOS ARIAS ANTONIO</t>
-  </si>
-  <si>
     <t>09-0397-03</t>
   </si>
   <si>
@@ -148,16 +136,16 @@
     <t>SILVA ROMERO JACQUELINE</t>
   </si>
   <si>
-    <t>09-0408-03</t>
-  </si>
-  <si>
-    <t>MEDINA ALVAREZ KARLA ITZEL</t>
-  </si>
-  <si>
     <t>09-0410-03</t>
   </si>
   <si>
     <t>CORREA MARTINEZ JOSE LUIS</t>
+  </si>
+  <si>
+    <t>09-0411-03</t>
+  </si>
+  <si>
+    <t>QUINTANA GONZALEZ URIEL</t>
   </si>
   <si>
     <t>15-0016-03</t>
@@ -576,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
@@ -744,7 +732,7 @@
         <v>29</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>352.19</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -766,7 +754,7 @@
         <v>33</v>
       </c>
       <c r="C17">
-        <v>352.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -898,28 +886,6 @@
         <v>57</v>
       </c>
       <c r="C29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31">
         <v>0</v>
       </c>
     </row>

--- a/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/monica_cruz_gifseguridad_com_mx/Documents/Escritorio/REPORTES DEDUCCIONES/DEDUCCIONESNOMINA2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5C8B74C-765D-469E-9D8E-4607FBD7DD8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{59C0633F-C6D9-4C3C-B289-8DFCBCDD4DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>09-0001-02</t>
   </si>
@@ -127,7 +127,7 @@
     <t>09-0406-03</t>
   </si>
   <si>
-    <t>RIVERA  FUENTES  EVELYN JAZMIN</t>
+    <t>RIVERA FUENTES EVELYN JAZMIN</t>
   </si>
   <si>
     <t>09-0407-03</t>
@@ -148,6 +148,12 @@
     <t>QUINTANA GONZALEZ URIEL</t>
   </si>
   <si>
+    <t>09-0412-03</t>
+  </si>
+  <si>
+    <t>SOTO SOLORZANO JOAQUIN</t>
+  </si>
+  <si>
     <t>15-0016-03</t>
   </si>
   <si>
@@ -188,6 +194,12 @@
   </si>
   <si>
     <t>SEVILLA MENDEZ JULIO CESAR</t>
+  </si>
+  <si>
+    <t>09-0326-03</t>
+  </si>
+  <si>
+    <t>MIGUEL GARCIA JULIAN</t>
   </si>
   <si>
     <t>09-0347-03</t>
@@ -564,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
@@ -886,6 +898,28 @@
         <v>57</v>
       </c>
       <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31">
         <v>0</v>
       </c>
     </row>

--- a/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/monica_cruz_gifseguridad_com_mx/Documents/Escritorio/REPORTES DEDUCCIONES/DEDUCCIONESNOMINA2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59C0633F-C6D9-4C3C-B289-8DFCBCDD4DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{870A6AA1-A4D6-4EC4-9AC4-C77C3CDD22A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>09-0001-02</t>
   </si>
@@ -130,22 +130,10 @@
     <t>RIVERA FUENTES EVELYN JAZMIN</t>
   </si>
   <si>
-    <t>09-0407-03</t>
-  </si>
-  <si>
-    <t>SILVA ROMERO JACQUELINE</t>
-  </si>
-  <si>
     <t>09-0410-03</t>
   </si>
   <si>
     <t>CORREA MARTINEZ JOSE LUIS</t>
-  </si>
-  <si>
-    <t>09-0411-03</t>
-  </si>
-  <si>
-    <t>QUINTANA GONZALEZ URIEL</t>
   </si>
   <si>
     <t>09-0412-03</t>
@@ -576,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
@@ -898,28 +886,6 @@
         <v>57</v>
       </c>
       <c r="C29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31">
         <v>0</v>
       </c>
     </row>

--- a/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/monica_cruz_gifseguridad_com_mx/Documents/Escritorio/REPORTES DEDUCCIONES/DEDUCCIONESNOMINA2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF14E48A-1E38-4DA0-ACB7-4A1EBD4E64D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1B33ADF-DE25-4C55-8EDD-75B4BA12C31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -154,10 +154,10 @@
     <t>OSORIO MIRANDA REYNA</t>
   </si>
   <si>
-    <t>15-0025-03</t>
-  </si>
-  <si>
-    <t>COLIN MENDEZ JUAN MANUEL</t>
+    <t>15-0026-03</t>
+  </si>
+  <si>
+    <t>ZACARIAS GARCIA MARELY</t>
   </si>
   <si>
     <t>09-0004-02</t>

--- a/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/monica_cruz_gifseguridad_com_mx/Documents/Escritorio/REPORTES DEDUCCIONES/DEDUCCIONESNOMINA2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1B33ADF-DE25-4C55-8EDD-75B4BA12C31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0CC11AC-F7DD-4484-A387-AE83ABA498EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>09-0001-02</t>
   </si>
@@ -148,16 +148,22 @@
     <t>MENDOZA CABALLERO GERARDO</t>
   </si>
   <si>
+    <t>09-0418-03</t>
+  </si>
+  <si>
+    <t>VALENCIA GARCIA GUSTAVO</t>
+  </si>
+  <si>
     <t>15-0016-03</t>
   </si>
   <si>
     <t>OSORIO MIRANDA REYNA</t>
   </si>
   <si>
-    <t>15-0026-03</t>
-  </si>
-  <si>
-    <t>ZACARIAS GARCIA MARELY</t>
+    <t>15-0027-03</t>
+  </si>
+  <si>
+    <t>GONZALEZ FLORES EDITH</t>
   </si>
   <si>
     <t>09-0004-02</t>
@@ -570,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
@@ -606,7 +612,7 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>438.81</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -903,6 +909,17 @@
         <v>59</v>
       </c>
       <c r="C30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31">
         <v>0</v>
       </c>
     </row>

--- a/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/monica_cruz_gifseguridad_com_mx/Documents/Escritorio/REPORTES DEDUCCIONES/DEDUCCIONESNOMINA2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E0CC11AC-F7DD-4484-A387-AE83ABA498EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC694CC3-4E4A-43DB-95F3-D75EE17FA4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>09-0001-02</t>
   </si>
@@ -100,12 +100,6 @@
     <t>BUSTAMANTE ARAGON OSCAR</t>
   </si>
   <si>
-    <t>09-0391-03</t>
-  </si>
-  <si>
-    <t>ITURBIDE JIMENEZ JUAN JESUS</t>
-  </si>
-  <si>
     <t>09-0397-03</t>
   </si>
   <si>
@@ -148,10 +142,22 @@
     <t>MENDOZA CABALLERO GERARDO</t>
   </si>
   <si>
-    <t>09-0418-03</t>
-  </si>
-  <si>
-    <t>VALENCIA GARCIA GUSTAVO</t>
+    <t>09-0419-03</t>
+  </si>
+  <si>
+    <t>RIVERA MEZA MARIA AURELIA</t>
+  </si>
+  <si>
+    <t>09-0420-03</t>
+  </si>
+  <si>
+    <t>LUZ GONZALEZ MARICRUZ</t>
+  </si>
+  <si>
+    <t>09-0421-03</t>
+  </si>
+  <si>
+    <t>HUERTA GUTIERREZ MARCO ANTONIO</t>
   </si>
   <si>
     <t>15-0016-03</t>
@@ -576,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
@@ -733,7 +739,7 @@
         <v>27</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>352.19</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -744,7 +750,7 @@
         <v>29</v>
       </c>
       <c r="C15">
-        <v>352.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -920,6 +926,17 @@
         <v>61</v>
       </c>
       <c r="C31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32">
         <v>0</v>
       </c>
     </row>

--- a/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/monica_cruz_gifseguridad_com_mx/Documents/Escritorio/REPORTES DEDUCCIONES/DEDUCCIONESNOMINA2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/monica_cruz_gifseguridad_com_mx/Documents/Escritorio/DEDUCCIONESFINIQUITO2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC694CC3-4E4A-43DB-95F3-D75EE17FA4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0915BBF7-19B4-4760-A23E-6459DA8542FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>09-0001-02</t>
   </si>
@@ -100,12 +100,6 @@
     <t>BUSTAMANTE ARAGON OSCAR</t>
   </si>
   <si>
-    <t>09-0397-03</t>
-  </si>
-  <si>
-    <t>VALLADARES PEREZ ALICIA</t>
-  </si>
-  <si>
     <t>09-0403-03</t>
   </si>
   <si>
@@ -136,12 +130,6 @@
     <t>SOTO SOLORZANO JOAQUIN</t>
   </si>
   <si>
-    <t>09-0416-03</t>
-  </si>
-  <si>
-    <t>MENDOZA CABALLERO GERARDO</t>
-  </si>
-  <si>
     <t>09-0419-03</t>
   </si>
   <si>
@@ -166,10 +154,10 @@
     <t>OSORIO MIRANDA REYNA</t>
   </si>
   <si>
-    <t>15-0027-03</t>
-  </si>
-  <si>
-    <t>GONZALEZ FLORES EDITH</t>
+    <t>15-0028-03</t>
+  </si>
+  <si>
+    <t>GUTIERREZ SALGADO AARON ALESSANDRO</t>
   </si>
   <si>
     <t>09-0004-02</t>
@@ -582,10 +570,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -739,7 +727,7 @@
         <v>27</v>
       </c>
       <c r="C14">
-        <v>352.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -915,28 +903,6 @@
         <v>59</v>
       </c>
       <c r="C30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32">
         <v>0</v>
       </c>
     </row>

--- a/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/monica_cruz_gifseguridad_com_mx/Documents/Escritorio/DEDUCCIONESFINIQUITO2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/monica_cruz_gifseguridad_com_mx/Documents/Escritorio/DEDUCCIONES 2026/DEDUCCIONES NOMINA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0915BBF7-19B4-4760-A23E-6459DA8542FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB6F1B5A-DEAA-4273-8A49-98DF62A578F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -142,10 +142,10 @@
     <t>LUZ GONZALEZ MARICRUZ</t>
   </si>
   <si>
-    <t>09-0421-03</t>
-  </si>
-  <si>
-    <t>HUERTA GUTIERREZ MARCO ANTONIO</t>
+    <t>09-0423-03</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ DAMIAN HUGO RICARDO</t>
   </si>
   <si>
     <t>15-0016-03</t>
@@ -172,12 +172,6 @@
     <t>SANTANA CHAVEZ SALVADOR</t>
   </si>
   <si>
-    <t>09-0160-03</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ HERNANDEZ DIONICIO</t>
-  </si>
-  <si>
     <t>09-0243-03</t>
   </si>
   <si>
@@ -200,6 +194,12 @@
   </si>
   <si>
     <t>RUIZ FUENTES DULCE GEOVANNY</t>
+  </si>
+  <si>
+    <t>09-0374-03</t>
+  </si>
+  <si>
+    <t>VEGA CORTEZ ABIGAIL</t>
   </si>
 </sst>
 </file>

--- a/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/fonacotNQUINCENAL .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/monica_cruz_gifseguridad_com_mx/Documents/Escritorio/DEDUCCIONES 2026/DEDUCCIONES NOMINA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB6F1B5A-DEAA-4273-8A49-98DF62A578F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{19BDFDB6-EB84-4EED-8CDE-18ACC9ED3ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
